--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_2_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_2_False.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Pg Vm Projection False</t>
   </si>
@@ -31,88 +31,85 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pd_tot</t>
+  </si>
+  <si>
     <t>pg_tot</t>
   </si>
   <si>
-    <t>pd_tot</t>
+    <t>sample_num</t>
   </si>
   <si>
     <t>qg_tot</t>
   </si>
   <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
     <t>Iinj_r_tot</t>
   </si>
   <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
     <t>Ibr_from_i_tot</t>
   </si>
   <si>
-    <t>qd_tot</t>
+    <t>vm_tot</t>
   </si>
   <si>
     <t>pinj_tot</t>
   </si>
   <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
-    <t>86999.64 (67239.59 &gt; 29.43%)</t>
-  </si>
-  <si>
-    <t>2.31 (1.28)</t>
-  </si>
-  <si>
-    <t>3.07s (6.66 s)</t>
-  </si>
-  <si>
-    <t>70203.52 (67239.59 &gt; 4.33%)</t>
-  </si>
-  <si>
-    <t>1.22 (1.28)</t>
-  </si>
-  <si>
-    <t>1.59s (6.66 s)</t>
-  </si>
-  <si>
-    <t>67235.75 (67239.59 &gt; 0.01%)</t>
-  </si>
-  <si>
-    <t>1.28 (1.28)</t>
-  </si>
-  <si>
-    <t>11.27s (6.66 s)</t>
-  </si>
-  <si>
-    <t>5.40s (6.66 s)</t>
+    <t>86992.75 (67239.59 &gt; 29.38%)</t>
+  </si>
+  <si>
+    <t>231.21 (128.36)</t>
+  </si>
+  <si>
+    <t>0.14s (0.15 s)</t>
+  </si>
+  <si>
+    <t>70238.66 (67239.59 &gt; 4.46%)</t>
+  </si>
+  <si>
+    <t>146.95 (128.36)</t>
+  </si>
+  <si>
+    <t>0.16s (0.15 s)</t>
+  </si>
+  <si>
+    <t>67206.13 (67239.59 &gt; 0.05%)</t>
+  </si>
+  <si>
+    <t>146.46 (128.36)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,16 +492,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.9319603443145752</v>
+        <v>0.5213097929954529</v>
       </c>
       <c r="C2">
-        <v>0.0270895529538393</v>
+        <v>0.5161948204040527</v>
       </c>
       <c r="D2">
-        <v>6.819956524850568E-06</v>
+        <v>0.5159370899200439</v>
       </c>
       <c r="E2">
-        <v>6.819956524850568E-06</v>
+        <v>0.5158597826957703</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,16 +509,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.383573394547226E-16</v>
+        <v>0.5431064963340759</v>
       </c>
       <c r="C3">
-        <v>1.383573394547226E-16</v>
+        <v>0.5376702547073364</v>
       </c>
       <c r="D3">
-        <v>1.383573394547226E-16</v>
+        <v>0.5373991131782532</v>
       </c>
       <c r="E3">
-        <v>1.383573394547226E-16</v>
+        <v>0.5373206734657288</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -529,33 +526,33 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.04098469763994217</v>
+        <v>0.000303947803331539</v>
       </c>
       <c r="C4">
-        <v>0.03418890759348869</v>
+        <v>2.954348019557074E-05</v>
       </c>
       <c r="D4">
-        <v>0.007782072760164738</v>
+        <v>0.000154962413944304</v>
       </c>
       <c r="E4">
-        <v>0.007782072760164738</v>
+        <v>0.00013980723451823</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
-        <v>0.3510844707489014</v>
-      </c>
-      <c r="C5">
-        <v>0.011526252143085</v>
-      </c>
-      <c r="D5">
-        <v>6.343716813717037E-05</v>
-      </c>
-      <c r="E5">
-        <v>6.343716813717037E-05</v>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,16 +560,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.01971029862761497</v>
+        <v>0.0008264003554359078</v>
       </c>
       <c r="C6">
-        <v>0.00765114463865757</v>
+        <v>0.0008264003554359078</v>
       </c>
       <c r="D6">
-        <v>0.001337802619673312</v>
+        <v>0.0008264003554359078</v>
       </c>
       <c r="E6">
-        <v>0.001337802619673312</v>
+        <v>2.638991862227734E-17</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -580,16 +577,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>2.638991862227734E-17</v>
+        <v>0.01945053227245808</v>
       </c>
       <c r="C7">
-        <v>2.638991862227734E-17</v>
+        <v>0.0002532619400881231</v>
       </c>
       <c r="D7">
-        <v>2.638991862227734E-17</v>
+        <v>0.0005908998427912593</v>
       </c>
       <c r="E7">
-        <v>2.638991862227734E-17</v>
+        <v>1.003163652057992E-05</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,16 +594,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.4276346862316132</v>
+        <v>0.002226050011813641</v>
       </c>
       <c r="C8">
-        <v>0.01254629250615835</v>
+        <v>0.002226050011813641</v>
       </c>
       <c r="D8">
-        <v>3.395861540411715E-06</v>
+        <v>0.002226050011813641</v>
       </c>
       <c r="E8">
-        <v>3.395861540411715E-06</v>
+        <v>1.383573394547226E-16</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -614,50 +611,38 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.02117450535297394</v>
+        <v>0.9449458718299866</v>
       </c>
       <c r="C9">
-        <v>0.0001124772970797494</v>
+        <v>0.04053464904427528</v>
       </c>
       <c r="D9">
-        <v>1.455546339457214E-06</v>
+        <v>0.01922374404966831</v>
       </c>
       <c r="E9">
-        <v>1.455546339457214E-06</v>
+        <v>0.0003103434864897281</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
-        <v>0.01950202509760857</v>
-      </c>
-      <c r="C10">
-        <v>0.007508507464081049</v>
-      </c>
-      <c r="D10">
-        <v>0.001334128202870488</v>
-      </c>
-      <c r="E10">
-        <v>0.001334128202870488</v>
-      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>8.717503806110471E-05</v>
+        <v>0.0671611949801445</v>
       </c>
       <c r="C11">
-        <v>2.178938484576065E-05</v>
+        <v>0.06447269022464752</v>
       </c>
       <c r="D11">
-        <v>1.049654019880109E-05</v>
+        <v>0.02398569695651531</v>
       </c>
       <c r="E11">
-        <v>1.049654019880109E-05</v>
+        <v>0.0201590321958065</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -665,33 +650,33 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.02167285420000553</v>
+        <v>0.102539449930191</v>
       </c>
       <c r="C12">
-        <v>0.01858494989573956</v>
+        <v>0.1021098792552948</v>
       </c>
       <c r="D12">
-        <v>0.006740090902894735</v>
+        <v>0.1020235642790794</v>
       </c>
       <c r="E12">
-        <v>0.006740090902894735</v>
+        <v>0.1020193696022034</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13">
-        <v>0.0001289525389438495</v>
-      </c>
-      <c r="C13">
-        <v>2.034992394328583E-05</v>
-      </c>
-      <c r="D13">
-        <v>9.979525202652439E-06</v>
-      </c>
-      <c r="E13">
-        <v>9.979525202652439E-06</v>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,33 +684,33 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.2828852236270905</v>
+        <v>0.3537632822990417</v>
       </c>
       <c r="C14">
-        <v>0.004201242700219154</v>
+        <v>0.01642782613635063</v>
       </c>
       <c r="D14">
-        <v>1.695444007054903E-05</v>
+        <v>0.009318864904344082</v>
       </c>
       <c r="E14">
-        <v>1.695444007054903E-05</v>
+        <v>0.0003714940685313195</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
+      <c r="B15">
+        <v>0.06521802395582199</v>
+      </c>
+      <c r="C15">
+        <v>0.06454058736562729</v>
+      </c>
+      <c r="D15">
+        <v>0.03734786063432693</v>
+      </c>
+      <c r="E15">
+        <v>0.03642543032765388</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -733,67 +718,84 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.0694473534822464</v>
+        <v>0.11240454018116</v>
       </c>
       <c r="C16">
-        <v>0.01761965453624725</v>
+        <v>0.06506401300430298</v>
       </c>
       <c r="D16">
-        <v>0.006158228497952223</v>
+        <v>0.03906203061342239</v>
       </c>
       <c r="E16">
-        <v>0.006158228497952223</v>
+        <v>0.0378761850297451</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17">
-        <v>0.2979118525981903</v>
-      </c>
-      <c r="C17">
-        <v>0.004291055258363485</v>
-      </c>
-      <c r="D17">
-        <v>1.702615372778382E-05</v>
-      </c>
-      <c r="E17">
-        <v>1.702615372778382E-05</v>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
+      <c r="B18">
+        <v>0.0880139023065567</v>
+      </c>
+      <c r="C18">
+        <v>0.08777596056461334</v>
+      </c>
+      <c r="D18">
+        <v>0.08761225640773773</v>
+      </c>
+      <c r="E18">
+        <v>0.08760794997215271</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
+      <c r="B19">
+        <v>0.0003399754350539297</v>
+      </c>
+      <c r="C19">
+        <v>2.880478314182255E-05</v>
+      </c>
+      <c r="D19">
+        <v>0.0001388387463521212</v>
+      </c>
+      <c r="E19">
+        <v>0.0001368455996271223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.434615820646286</v>
+      </c>
+      <c r="C20">
+        <v>0.01875392347574234</v>
+      </c>
+      <c r="D20">
+        <v>0.01076088473200798</v>
+      </c>
+      <c r="E20">
+        <v>0.0004256545216776431</v>
       </c>
     </row>
   </sheetData>
